--- a/ListaRequisitos.xlsx
+++ b/ListaRequisitos.xlsx
@@ -51,12 +51,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -71,8 +83,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -362,19 +376,19 @@
     <col min="4" max="4" width="32.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
